--- a/data/trans_orig/P57B6_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B6_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido tranquilo/a y relajado/a en 2023</t>
+          <t>Población según se ha sentido tranquilo/a y relajado/a en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21728</t>
+          <t>21785</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54905</t>
+          <t>53635</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>19778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34860</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67780</t>
+          <t>67840</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>245433</t>
+          <t>244311</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278603</t>
+          <t>278295</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248561</t>
+          <t>247559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>266002</t>
+          <t>265323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>503288</t>
+          <t>502288</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>539443</t>
+          <t>538641</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20649</t>
+          <t>19643</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>11749</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24779</t>
+          <t>26397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>18755</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>38383</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>491</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>265998</t>
+          <t>265809</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>326034</t>
+          <t>323697</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>197327</t>
+          <t>197209</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>235497</t>
+          <t>236813</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>478303</t>
+          <t>481896</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>551636</t>
+          <t>552347</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134212</t>
+          <t>133113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>190794</t>
+          <t>185223</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>174033</t>
+          <t>174522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>211817</t>
+          <t>211818</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>317770</t>
+          <t>318152</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>384934</t>
+          <t>384744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,45%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29037</t>
+          <t>28383</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59884</t>
+          <t>59802</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70207</t>
+          <t>70290</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99611</t>
+          <t>98322</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105739</t>
+          <t>106183</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149429</t>
+          <t>145603</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9291</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29567</t>
+          <t>29031</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12702</t>
+          <t>12230</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28978</t>
+          <t>28274</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25590</t>
+          <t>25997</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51594</t>
+          <t>52223</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158754</t>
+          <t>157329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>192135</t>
+          <t>192598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138180</t>
+          <t>138145</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>169711</t>
+          <t>170081</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>308250</t>
+          <t>306817</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>353923</t>
+          <t>353280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,24%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92906</t>
+          <t>92240</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>123634</t>
+          <t>125571</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>113341</t>
+          <t>113885</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>144120</t>
+          <t>143298</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>213519</t>
+          <t>214294</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>257491</t>
+          <t>256466</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19496</t>
+          <t>19289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39462</t>
+          <t>39782</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37879</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58610</t>
+          <t>59447</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62855</t>
+          <t>64103</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90098</t>
+          <t>91399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>11069</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25808</t>
+          <t>25676</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14663</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31158</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>131359</t>
+          <t>131589</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>177556</t>
+          <t>174833</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83429</t>
+          <t>77349</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>170655</t>
+          <t>173985</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>205237</t>
+          <t>204111</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>335643</t>
+          <t>338326</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83690</t>
+          <t>83932</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125659</t>
+          <t>123553</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>159339</t>
+          <t>157793</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>316975</t>
+          <t>322576</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>264450</t>
+          <t>262076</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>457888</t>
+          <t>448549</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>57,68%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37761</t>
+          <t>38135</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>66137</t>
+          <t>68479</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60308</t>
+          <t>61651</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>126189</t>
+          <t>126140</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>103145</t>
+          <t>108455</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>177742</t>
+          <t>177340</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18854</t>
+          <t>18955</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24036</t>
+          <t>22561</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37307</t>
+          <t>35408</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>21927</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30349</t>
+          <t>30499</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>52722</t>
+          <t>53838</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70552</t>
+          <t>70557</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93101</t>
+          <t>92963</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71562</t>
+          <t>70664</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>91813</t>
+          <t>90851</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>147767</t>
+          <t>146584</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>177999</t>
+          <t>176822</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60398</t>
+          <t>59610</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>82306</t>
+          <t>82027</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>98209</t>
+          <t>99027</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>118240</t>
+          <t>119556</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>165315</t>
+          <t>165270</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>194699</t>
+          <t>195487</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>118964</t>
+          <t>121319</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>150675</t>
+          <t>152741</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>105742</t>
+          <t>103214</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>128316</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>234003</t>
+          <t>234684</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>273693</t>
+          <t>273734</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,97%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>93627</t>
+          <t>91272</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>122703</t>
+          <t>121363</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>79906</t>
+          <t>79859</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>102675</t>
+          <t>104321</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>178831</t>
+          <t>177764</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>216287</t>
+          <t>214970</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14507</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>28541</t>
+          <t>27567</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>33756</t>
+          <t>33726</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52045</t>
+          <t>51641</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>52427</t>
+          <t>52087</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>74788</t>
+          <t>74871</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>11008</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>219188</t>
+          <t>216628</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>279907</t>
+          <t>279418</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>97378</t>
+          <t>91773</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>250149</t>
+          <t>250665</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>262557</t>
+          <t>278090</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>513316</t>
+          <t>516190</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>233770</t>
+          <t>232124</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>291611</t>
+          <t>291011</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>370193</t>
+          <t>367602</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>650175</t>
+          <t>669661</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>621614</t>
+          <t>623650</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1030963</t>
+          <t>1008543</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>68,44%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>75782</t>
+          <t>74535</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>114859</t>
+          <t>115076</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>75764</t>
+          <t>68224</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>192567</t>
+          <t>193052</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>144531</t>
+          <t>149660</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>282082</t>
+          <t>280337</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14627</t>
+          <t>14677</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>34455</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>15860</t>
+          <t>15616</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>49214</t>
+          <t>49935</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>34376</t>
+          <t>36267</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>74171</t>
+          <t>75258</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>377818</t>
+          <t>379126</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>749796</t>
+          <t>749897</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>219668</t>
+          <t>220239</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>265219</t>
+          <t>262927</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>606695</t>
+          <t>606241</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1092212</t>
+          <t>1113758</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>114088</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>365673</t>
+          <t>365725</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>268030</t>
+          <t>268033</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>312228</t>
+          <t>310753</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>350003</t>
+          <t>339934</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>658797</t>
+          <t>660075</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>49186</t>
+          <t>51341</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>165658</t>
+          <t>168489</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>149356</t>
+          <t>148246</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>187572</t>
+          <t>188800</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>181687</t>
+          <t>173509</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>344477</t>
+          <t>344908</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>28806</t>
+          <t>30998</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>15217</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>30161</t>
+          <t>29761</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>24213</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>54449</t>
+          <t>54191</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1441229</t>
+          <t>1438132</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2037692</t>
+          <t>2033608</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>863945</t>
+          <t>870466</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1166183</t>
+          <t>1178093</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2437103</t>
+          <t>2426709</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3169589</t>
+          <t>3146648</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,32%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1015563</t>
+          <t>1025184</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1465567</t>
+          <t>1466512</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1611689</t>
+          <t>1598905</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2115945</t>
+          <t>2131137</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,17 +5460,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>3099078</t>
+          <t>3099079</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2798712</t>
+          <t>2799199</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3414110</t>
+          <t>3491270</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>335889</t>
+          <t>330959</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>484064</t>
+          <t>488097</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>574740</t>
+          <t>569020</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>766299</t>
+          <t>770538</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>998685</t>
+          <t>984445</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1232608</t>
+          <t>1235354</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>52758</t>
+          <t>53257</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>93915</t>
+          <t>92291</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>89774</t>
+          <t>94329</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>133728</t>
+          <t>133989</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>157139</t>
+          <t>153923</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>216010</t>
+          <t>214137</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7100303</t>
+          <t>7100304</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7100303</t>
+          <t>7100304</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7100303</t>
+          <t>7100304</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">

--- a/data/trans_orig/P57B6_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B6_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32667</t>
+          <t>33302</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21785</t>
+          <t>23146</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53635</t>
+          <t>43678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>16944</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19778</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46495</t>
+          <t>50245</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67840</t>
+          <t>64952</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>265675</t>
+          <t>272143</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244311</t>
+          <t>257805</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278295</t>
+          <t>282558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>258026</t>
+          <t>279290</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247559</t>
+          <t>269250</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265323</t>
+          <t>287280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>523701</t>
+          <t>551432</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>502288</t>
+          <t>535486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>538641</t>
+          <t>565378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16704</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>13539</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26397</t>
+          <t>27158</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>27492</t>
+          <t>30240</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18755</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38383</t>
+          <t>40990</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>871</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,57 +1074,57 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3818</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1076</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3817</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>493</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>297635</t>
+          <t>299637</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>265809</t>
+          <t>269548</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>323697</t>
+          <t>328208</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>216734</t>
+          <t>230490</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>197209</t>
+          <t>210403</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>236813</t>
+          <t>251594</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>514368</t>
+          <t>530127</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>481896</t>
+          <t>494736</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>552347</t>
+          <t>564763</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>52,7%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>158483</t>
+          <t>166923</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133113</t>
+          <t>142321</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>185223</t>
+          <t>196599</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>192845</t>
+          <t>208082</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>174522</t>
+          <t>189867</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>211818</t>
+          <t>228406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>351328</t>
+          <t>375005</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>318152</t>
+          <t>342746</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>384744</t>
+          <t>408973</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41391</t>
+          <t>43755</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28383</t>
+          <t>30913</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59802</t>
+          <t>61999</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84159</t>
+          <t>86453</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70290</t>
+          <t>72684</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98322</t>
+          <t>101589</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>125550</t>
+          <t>130208</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106183</t>
+          <t>111653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145603</t>
+          <t>151512</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29031</t>
+          <t>29077</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19465</t>
+          <t>19593</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12230</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>27753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>36136</t>
+          <t>36315</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25997</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52223</t>
+          <t>50754</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>514180</t>
+          <t>527037</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>514180</t>
+          <t>527037</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>514180</t>
+          <t>527037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>513203</t>
+          <t>544617</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>513203</t>
+          <t>544617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>513203</t>
+          <t>544617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1027382</t>
+          <t>1071654</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1027382</t>
+          <t>1071654</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1027382</t>
+          <t>1071654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>175520</t>
+          <t>175231</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157329</t>
+          <t>158392</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>192598</t>
+          <t>192480</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>155398</t>
+          <t>157889</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138145</t>
+          <t>140963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170081</t>
+          <t>173821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>330918</t>
+          <t>333120</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>306817</t>
+          <t>308965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>353280</t>
+          <t>356861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,19%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>107841</t>
+          <t>107999</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92240</t>
+          <t>92648</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125571</t>
+          <t>124452</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,27 +2011,27 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>127768</t>
+          <t>131165</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>113885</t>
+          <t>116068</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>143298</t>
+          <t>146288</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>235609</t>
+          <t>239164</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>214294</t>
+          <t>217635</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>256466</t>
+          <t>261610</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27993</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>19881</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39782</t>
+          <t>38666</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>47809</t>
+          <t>48105</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38744</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59447</t>
+          <t>58657</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>75802</t>
+          <t>76228</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64103</t>
+          <t>62108</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91399</t>
+          <t>89443</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -2202,22 +2202,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>18665</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11069</t>
+          <t>12738</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25676</t>
+          <t>27197</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>22372</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>32713</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>315046</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>315046</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>315046</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>348576</t>
+          <t>355824</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>348576</t>
+          <t>355824</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>348576</t>
+          <t>355824</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>663622</t>
+          <t>670883</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>663622</t>
+          <t>670883</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>663622</t>
+          <t>670883</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>153308</t>
+          <t>187700</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>131589</t>
+          <t>164100</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>174833</t>
+          <t>212628</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>134103</t>
+          <t>152972</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77349</t>
+          <t>133482</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>173985</t>
+          <t>174531</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>287411</t>
+          <t>340672</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>204111</t>
+          <t>310580</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>338326</t>
+          <t>378834</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>102501</t>
+          <t>124312</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83932</t>
+          <t>100745</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123553</t>
+          <t>147758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>224402</t>
+          <t>139570</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>157793</t>
+          <t>120574</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>322576</t>
+          <t>159983</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>326903</t>
+          <t>263882</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>262076</t>
+          <t>234710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>448549</t>
+          <t>295339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51039</t>
+          <t>54732</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38135</t>
+          <t>39972</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>68479</t>
+          <t>72855</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>98196</t>
+          <t>108965</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61651</t>
+          <t>94203</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>126140</t>
+          <t>128463</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>149235</t>
+          <t>163697</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>108455</t>
+          <t>141638</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>177340</t>
+          <t>188201</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>15564</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18955</t>
+          <t>20172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14064</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22561</t>
+          <t>25034</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>309744</t>
+          <t>370061</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>309744</t>
+          <t>370061</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>309744</t>
+          <t>370061</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>467868</t>
+          <t>413555</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>467868</t>
+          <t>413555</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>467868</t>
+          <t>413555</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>777612</t>
+          <t>783616</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>777612</t>
+          <t>783616</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>777612</t>
+          <t>783616</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25191</t>
+          <t>29160</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>19692</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35408</t>
+          <t>41036</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>17221</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21927</t>
+          <t>26287</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>40311</t>
+          <t>46381</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30499</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53838</t>
+          <t>60404</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>81223</t>
+          <t>95370</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70557</t>
+          <t>81399</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92963</t>
+          <t>107418</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>81157</t>
+          <t>89858</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70664</t>
+          <t>78965</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90851</t>
+          <t>100966</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>162379</t>
+          <t>185228</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>146584</t>
+          <t>167543</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>176822</t>
+          <t>201476</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>70571</t>
+          <t>78758</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59610</t>
+          <t>66840</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>82027</t>
+          <t>91630</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>108723</t>
+          <t>116010</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>99027</t>
+          <t>104946</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>119556</t>
+          <t>127437</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>179293</t>
+          <t>194769</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>165270</t>
+          <t>178677</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>195487</t>
+          <t>211562</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>177667</t>
+          <t>204554</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>177667</t>
+          <t>204554</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>177667</t>
+          <t>204554</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>207537</t>
+          <t>226048</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>207537</t>
+          <t>226048</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>207537</t>
+          <t>226048</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>385204</t>
+          <t>430602</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>385204</t>
+          <t>430602</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>385204</t>
+          <t>430602</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>135859</t>
+          <t>134143</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>121319</t>
+          <t>118238</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>152741</t>
+          <t>148653</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>117821</t>
+          <t>119632</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>103214</t>
+          <t>105422</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>128316</t>
+          <t>132492</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>253680</t>
+          <t>253775</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>234684</t>
+          <t>235101</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>273734</t>
+          <t>273267</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,13%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>107213</t>
+          <t>110362</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>91272</t>
+          <t>95814</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>121363</t>
+          <t>124088</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>90232</t>
+          <t>93758</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>79859</t>
+          <t>81402</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>104321</t>
+          <t>105429</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>197445</t>
+          <t>204120</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>177764</t>
+          <t>185983</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>214970</t>
+          <t>222844</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,7%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>20285</t>
+          <t>20030</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>13833</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27567</t>
+          <t>27137</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>42182</t>
+          <t>43537</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>33726</t>
+          <t>35603</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>51641</t>
+          <t>53172</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>62466</t>
+          <t>63568</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>52087</t>
+          <t>53113</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>74871</t>
+          <t>75636</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>11199</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>247846</t>
+          <t>282465</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>216628</t>
+          <t>252434</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>279418</t>
+          <t>314693</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>183291</t>
+          <t>223319</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>91773</t>
+          <t>199514</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>250665</t>
+          <t>247433</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>431137</t>
+          <t>505784</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>278090</t>
+          <t>464053</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>516190</t>
+          <t>543075</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>260269</t>
+          <t>305599</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>232124</t>
+          <t>274523</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>291011</t>
+          <t>336372</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>491534</t>
+          <t>337673</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>367602</t>
+          <t>311543</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>669661</t>
+          <t>366466</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>751803</t>
+          <t>643272</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>623650</t>
+          <t>608330</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1008543</t>
+          <t>690623</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>93553</t>
+          <t>108280</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>74535</t>
+          <t>88432</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>115076</t>
+          <t>131593</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>140089</t>
+          <t>169092</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>68224</t>
+          <t>147325</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>193052</t>
+          <t>190835</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>233642</t>
+          <t>277372</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>149660</t>
+          <t>249389</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>280337</t>
+          <t>309035</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>22610</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>34455</t>
+          <t>35677</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>34352</t>
+          <t>41973</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>15616</t>
+          <t>30571</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>49935</t>
+          <t>52715</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>56962</t>
+          <t>65316</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>36267</t>
+          <t>50653</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>75258</t>
+          <t>80707</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>532290</t>
+          <t>343532</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>379126</t>
+          <t>313746</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>749897</t>
+          <t>373552</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>241177</t>
+          <t>281052</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>220239</t>
+          <t>254653</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>262927</t>
+          <t>306442</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>773468</t>
+          <t>624584</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>606241</t>
+          <t>585890</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1113758</t>
+          <t>661681</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>261347</t>
+          <t>302078</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>120401</t>
+          <t>271410</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>365725</t>
+          <t>331069</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>288564</t>
+          <t>337183</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>268033</t>
+          <t>312863</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>310753</t>
+          <t>365001</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>549911</t>
+          <t>639261</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>339934</t>
+          <t>600439</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>660075</t>
+          <t>675445</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>41,45%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>116603</t>
+          <t>130308</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>51341</t>
+          <t>108928</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>168489</t>
+          <t>154211</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>166780</t>
+          <t>188803</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>148246</t>
+          <t>167949</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>188800</t>
+          <t>211159</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>283384</t>
+          <t>319111</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>173509</t>
+          <t>289523</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>344908</t>
+          <t>349502</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>18479</t>
+          <t>22153</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>30998</t>
+          <t>32843</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,22 +5082,22 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>21210</t>
+          <t>24293</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>16827</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>29761</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>39689</t>
+          <t>46446</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>24187</t>
+          <t>34918</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>54191</t>
+          <t>61448</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1600317</t>
+          <t>1485169</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1438132</t>
+          <t>1422560</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2033608</t>
+          <t>1554014</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1077472</t>
+          <t>1199519</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>870466</t>
+          <t>1147101</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1178093</t>
+          <t>1251858</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2677789</t>
+          <t>2684688</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2426709</t>
+          <t>2595396</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3146648</t>
+          <t>2768743</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>38,21%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1344552</t>
+          <t>1484787</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1025184</t>
+          <t>1425522</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1466512</t>
+          <t>1553364</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1754527</t>
+          <t>1616578</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1598905</t>
+          <t>1563148</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2131137</t>
+          <t>1668082</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>3099079</t>
+          <t>3101365</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2799199</t>
+          <t>3016646</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3491270</t>
+          <t>3191830</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>44,05%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>432223</t>
+          <t>475437</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>330959</t>
+          <t>433688</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>488097</t>
+          <t>518150</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>704641</t>
+          <t>779756</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>569020</t>
+          <t>740827</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>770538</t>
+          <t>823591</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1136864</t>
+          <t>1255193</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>984445</t>
+          <t>1195819</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1235354</t>
+          <t>1318389</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>72342</t>
+          <t>77551</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>53257</t>
+          <t>59849</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>92291</t>
+          <t>98600</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>114230</t>
+          <t>127390</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>94329</t>
+          <t>110881</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>133989</t>
+          <t>150211</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>186572</t>
+          <t>204942</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>153923</t>
+          <t>178611</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>214137</t>
+          <t>235062</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3449434</t>
+          <t>3522944</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3449434</t>
+          <t>3522944</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3449434</t>
+          <t>3522944</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3650870</t>
+          <t>3723244</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3650870</t>
+          <t>3723244</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3650870</t>
+          <t>3723244</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7100304</t>
+          <t>7246188</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7100304</t>
+          <t>7246188</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7100304</t>
+          <t>7246188</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
